--- a/data/plantillas/plantilla_propiedades.xlsx
+++ b/data/plantillas/plantilla_propiedades.xlsx
@@ -526,7 +526,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Plantilla de propiedades — IA Corredor</t>
+          <t>Plantilla de propiedades — AgentSales</t>
         </is>
       </c>
     </row>

--- a/data/plantillas/plantilla_propiedades.xlsx
+++ b/data/plantillas/plantilla_propiedades.xlsx
@@ -1590,7 +1590,7 @@
       </c>
       <c r="C49" s="5" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D49" s="5" t="inlineStr">
@@ -1605,7 +1605,7 @@
       </c>
       <c r="F49" s="5" t="inlineStr">
         <is>
-          <t>Link a carpeta de Google Drive o nombre de la carpeta local con fotos y videos.</t>
+          <t>Link a carpeta de Google Drive o nombre de la carpeta local con fotos y videos. Si se deja vacía, se usa id_propiedad.</t>
         </is>
       </c>
     </row>
@@ -1991,7 +1991,7 @@
           <t>requisitos_arriendo</t>
         </is>
       </c>
-      <c r="AD1" s="6" t="inlineStr">
+      <c r="AD1" s="7" t="inlineStr">
         <is>
           <t>carpeta_medios</t>
         </is>
